--- a/execl/attr.xlsx
+++ b/execl/attr.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="26295" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="attr" sheetId="1" r:id="rId1"/>
+    <sheet name="skillAttr" sheetId="2" r:id="rId2"/>
+    <sheet name="buffAttr" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="124">
   <si>
     <t>表格名称</t>
   </si>
@@ -43,6 +45,9 @@
   <si>
     <t>1=绝对值
 2=万分比</t>
+  </si>
+  <si>
+    <t>不填就是全局。填就是指向某个标签</t>
   </si>
   <si>
     <t>玩家基础属性</t>
@@ -68,6 +73,9 @@
     <t>字段类型</t>
   </si>
   <si>
+    <t>作用类型</t>
+  </si>
+  <si>
     <t>字段初始</t>
   </si>
   <si>
@@ -92,6 +100,9 @@
     <t>type</t>
   </si>
   <si>
+    <t>actType</t>
+  </si>
+  <si>
     <t>base</t>
   </si>
   <si>
@@ -224,6 +235,9 @@
     <t>物理伤害</t>
   </si>
   <si>
+    <t>物理系</t>
+  </si>
+  <si>
     <t>stat_14</t>
   </si>
   <si>
@@ -233,6 +247,9 @@
     <t>风系伤害</t>
   </si>
   <si>
+    <t>风系</t>
+  </si>
+  <si>
     <t>stat_15</t>
   </si>
   <si>
@@ -242,6 +259,9 @@
     <t>冰系伤害</t>
   </si>
   <si>
+    <t>冰系</t>
+  </si>
+  <si>
     <t>stat_16</t>
   </si>
   <si>
@@ -251,6 +271,9 @@
     <t>火系伤害</t>
   </si>
   <si>
+    <t>火系</t>
+  </si>
+  <si>
     <t>stat_17</t>
   </si>
   <si>
@@ -260,6 +283,9 @@
     <t>电系伤害</t>
   </si>
   <si>
+    <t>电系</t>
+  </si>
+  <si>
     <t>stat_18</t>
   </si>
   <si>
@@ -336,6 +362,48 @@
   </si>
   <si>
     <t>技能攻击</t>
+  </si>
+  <si>
+    <t>技能参数</t>
+  </si>
+  <si>
+    <t>弹道类数量增加</t>
+  </si>
+  <si>
+    <t>弹道类</t>
+  </si>
+  <si>
+    <t>弹道类伤害</t>
+  </si>
+  <si>
+    <t>激光范围</t>
+  </si>
+  <si>
+    <t>激光类</t>
+  </si>
+  <si>
+    <t>buff参数</t>
+  </si>
+  <si>
+    <t>燃烧伤害</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>燃烧持续时间</t>
+  </si>
+  <si>
+    <t>麻痹时间</t>
+  </si>
+  <si>
+    <t>麻痹</t>
+  </si>
+  <si>
+    <t>冷冻伤害</t>
+  </si>
+  <si>
+    <t>冷冻</t>
   </si>
 </sst>
 </file>
@@ -976,26 +1044,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1311,625 +1379,1120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.375" style="1" customWidth="1"/>
-    <col min="9" max="16383" width="9" style="1"/>
+    <col min="1" max="1" width="9.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="8.375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="18.375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="34.75" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" ht="57" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="6" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="57" spans="1:9">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3" t="s">
+      <c r="G4" s="1"/>
+      <c r="H4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3" t="s">
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="G7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
         <v>1000</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="G9" s="1"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="3">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="3">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
         <v>50</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="1">
         <v>50</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="3">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="3">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="3">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
         <v>50</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="1">
         <v>50</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="H14" s="2"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="3">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="3">
+        <v>49</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="3">
+        <v>52</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="3">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1">
         <v>2</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
         <v>15000</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="G18" s="1"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="3">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="1">
         <v>2</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="3">
+        <v>61</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="1">
         <v>2</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="3">
+        <v>64</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="1">
         <v>2</v>
       </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="3">
+        <v>68</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="1">
         <v>2</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="E22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="3">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="1">
         <v>2</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="3">
-        <v>2</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="1">
         <v>1</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="3">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="5"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="14.25" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="142.5" spans="1:9">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" ht="14.25" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="14.25" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="C10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="14.25" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="171" spans="1:9">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" ht="14.25" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="14.25" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="C11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>